--- a/Project 3 Comments.xlsx
+++ b/Project 3 Comments.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livecsupomona-my.sharepoint.com/personal/juanfestrada_cpp_edu/Documents/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livecsupomona-my.sharepoint.com/personal/juanfestrada_cpp_edu/Documents/Documents/project-1-a-journey/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="8_{2FDC49F7-5335-4EED-87DF-E63740CA2F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A83B7AB-A8BA-4A89-B786-FA0992D04EAC}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{2FDC49F7-5335-4EED-87DF-E63740CA2F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC2B01AB-725F-4102-8356-831E59DB762D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3FB06D55-76BF-4FA7-B1A7-2BFA49894AB8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
   <si>
     <t>Group A - Mafia</t>
   </si>
@@ -48,42 +48,6 @@
   </si>
   <si>
     <t>Juan Estrada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 8 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 - </t>
   </si>
   <si>
     <t xml:space="preserve">13 - </t>
@@ -409,6 +373,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -753,167 +721,167 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="316.8" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="244.8" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="316.8" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.3">
@@ -922,169 +890,79 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
